--- a/docentes/Silva Villegas Mario - Estadisticos 20222.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="82">
   <si>
     <t>Mat</t>
   </si>
@@ -76,22 +76,193 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>COSCAHUA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MACIEL</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>TAMAYO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>AVENDAÑO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>JACOBO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>ATENOGENES</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
   </si>
   <si>
     <t>BERISTAIN</t>
   </si>
   <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
     <t>MONTERO</t>
   </si>
   <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>JUAN DIEGO</t>
+  </si>
+  <si>
+    <t>JOSE DAMIAN</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>VICTOR ISRAEL</t>
+  </si>
+  <si>
+    <t>DAVID DANIEL</t>
+  </si>
+  <si>
+    <t>JOSE EDUARDO</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
+    <t>GERSON UZIEL</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>JOSMAR JAHIR</t>
+  </si>
+  <si>
+    <t>AXEL JESUS</t>
+  </si>
+  <si>
+    <t>KARLA JOVANA</t>
+  </si>
+  <si>
     <t>LUIS ENRIQUE</t>
   </si>
   <si>
+    <t>CRISTIAN JAHIR</t>
+  </si>
+  <si>
     <t>ALEXIS YAIR</t>
+  </si>
+  <si>
+    <t>JOHAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JORGE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
   </si>
 </sst>
 </file>
@@ -773,7 +944,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -805,22 +976,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920014</v>
+        <v>21330051920008</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -828,22 +999,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920014</v>
+        <v>21330051920010</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -851,22 +1022,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920067</v>
+        <v>21330051920011</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -874,24 +1045,645 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
+        <v>21330051920013</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920391</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920015</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920016</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920022</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920367</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920018</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920019</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920021</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920022</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920025</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920027</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920041</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920041</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920359</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920359</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>19330051920014</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>19330051920014</v>
+      </c>
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920081</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920081</v>
+      </c>
+      <c r="B24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
         <v>19330051920067</v>
       </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="B25" t="s">
         <v>24</v>
       </c>
-      <c r="E5" t="s">
+      <c r="C25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>19330051920067</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" t="s">
         <v>10</v>
       </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
+      <c r="F26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>20330051920093</v>
+      </c>
+      <c r="B27" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>20330051920093</v>
+      </c>
+      <c r="B28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920064</v>
+      </c>
+      <c r="B29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>20330051920064</v>
+      </c>
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>20330051920070</v>
+      </c>
+      <c r="B31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" t="s">
+        <v>81</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>20330051920070</v>
+      </c>
+      <c r="B32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Silva Villegas Mario - Estadisticos 20222.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -76,19 +76,34 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MIXCOA</t>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
   </si>
   <si>
     <t>MONTERO</t>
   </si>
   <si>
-    <t>JOSE EDUARDO</t>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
   </si>
   <si>
     <t>ALEXIS YAIR</t>
@@ -609,16 +624,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>66.67</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -632,16 +650,19 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>68.18000000000001</v>
+      </c>
+      <c r="H3">
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -655,16 +676,19 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>77.27</v>
+      </c>
+      <c r="H4">
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>
@@ -720,16 +744,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -746,13 +770,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>77.27</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="H3">
         <v>6.5</v>
@@ -781,7 +805,7 @@
         <v>77.27</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -791,7 +815,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -823,16 +847,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920022</v>
+        <v>20330051920366</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -841,29 +865,75 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920067</v>
+        <v>21330051920013</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920014</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920067</v>
+      </c>
+      <c r="B5" t="s">
         <v>22</v>
       </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F5" t="s">
         <v>12</v>
       </c>
-      <c r="G3">
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Silva Villegas Mario - Estadisticos 20222.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20222.xlsx
@@ -76,12 +76,12 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
     <t>NAJERA</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
@@ -97,10 +97,10 @@
     <t>MONTERO</t>
   </si>
   <si>
+    <t>OMAR</t>
+  </si>
+  <si>
     <t>ELI ANTONIO</t>
-  </si>
-  <si>
-    <t>OMAR</t>
   </si>
   <si>
     <t>LUIS ENRIQUE</t>
@@ -847,13 +847,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920366</v>
+        <v>21330051920013</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
         <v>26</v>
@@ -870,13 +870,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920013</v>
+        <v>20330051920366</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
         <v>27</v>
@@ -888,7 +888,7 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">

--- a/docentes/Silva Villegas Mario - Estadisticos 20222.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -76,31 +76,49 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>URBINA</t>
+  </si>
+  <si>
     <t>BERISTAIN</t>
   </si>
   <si>
     <t>MONTERO</t>
   </si>
   <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>ALDIR ADALBERTO</t>
+  </si>
+  <si>
     <t>OMAR</t>
-  </si>
-  <si>
-    <t>ELI ANTONIO</t>
   </si>
   <si>
     <t>LUIS ENRIQUE</t>
@@ -815,7 +833,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -847,16 +865,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920013</v>
+        <v>21330051920003</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -876,10 +894,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -893,16 +911,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920014</v>
+        <v>20330051920065</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -911,29 +929,75 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920067</v>
+        <v>21330051920013</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>19330051920014</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920067</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
         <v>29</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
         <v>10</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F7" t="s">
         <v>12</v>
       </c>
-      <c r="G5">
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Silva Villegas Mario - Estadisticos 20222.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -76,52 +76,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
     <t>MONTERO</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>ELI ANTONIO</t>
-  </si>
-  <si>
-    <t>ALDIR ADALBERTO</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
   </si>
   <si>
     <t>ALEXIS YAIR</t>
@@ -762,16 +720,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>66.67</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -788,16 +746,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>68.18000000000001</v>
+        <v>86.36</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -814,13 +772,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>77.27</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H4">
         <v>6.3</v>
@@ -833,7 +791,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -865,139 +823,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920003</v>
+        <v>19330051920067</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920366</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920065</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920013</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920014</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920067</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
         <v>1</v>
       </c>
     </row>
